--- a/output/excel/10K-GOOG-01-31-2024_classified.xlsx
+++ b/output/excel/10K-GOOG-01-31-2024_classified.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_BalanceSheet_alphabet_inc_co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_BalanceSheet_balancesheet" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="02_IncomeStatement_alphabet_inc" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="03_ComprehensiveIncome_alphabet" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="04_Equity_alphabet_inc_consolid" sheetId="4" state="visible" r:id="rId4"/>
@@ -89,6 +89,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -99,12 +105,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Alphabet Inc. CONSOLIDATED BALANCE SHEETS (in millions, except par value per share amounts) — Alphabet Inc.  (in in millions, except par value per share amounts)</t>
+          <t>BalanceSheet</t>
         </is>
       </c>
     </row>
@@ -511,604 +511,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Current assets:</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total current assets</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>164,795</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>171,530</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Non-marketable securities</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>30,492</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>31,008</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Deferred income taxes</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>5,261</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>12,169</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Property and equipment, net</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>112,668</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>134,345</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Operating lease assets</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>14,381</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>14,091</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Goodwill</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>28,960</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>29,198</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Other non-current assets</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>8,707</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>10,051</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>$21,879</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>$24,048</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Marketable securities</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>91,883</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>86,868</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Total cash, cash equivalents, and marketable securities</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>113,762</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>110,916</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accounts receivable, net</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>40,258</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>47,964</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Other current assets</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>10,775</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>12,650</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>$365,264</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>$402,392</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities and Stockholders' Equity</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Current liabilities:</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total current liabilities</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>69,300</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>81,814</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Long-term debt</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>14,701</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>13,253</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Deferred revenue, non-current</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Income taxes payable, non-current</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>9,258</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>8,474</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Deferred income taxes</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Operating lease liabilities</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>12,501</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>12,460</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Other long-term liabilities</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>2,247</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>1,616</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accounts payable</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>$5,128</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>$7,493</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accrued compensation and benefits</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>14,028</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>15,140</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accrued expenses and other current liabilities</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>37,866</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>46,168</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accrued revenue share</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>8,370</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>8,876</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Deferred revenue</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>3,908</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>4,137</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>109,120</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>119,013</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Commitments and Contingencies (Note 10)</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr"/>
-      <c r="C34" s="10" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Stockholders' equity:</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr"/>
-      <c r="C35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Preferred stock, $0.001 par value per share, 100 shares authorized; no shares issued and outstanding</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Class A, Class B, and Class C stock and additional paid-in capital, $0.001 par value per share: 300,000 shares authorized (Class A 180,000, Class B 60.000. Class C 60,000); 12,849 (Class A 5,964, Class B 883, Class C 6,002) and 12,460 (Class A 5,899, Class B 870, Class C 5,691) shares issued and outstanding</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>68,184</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>76,534</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Accumulated other comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>(7,603)</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>(4,402)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Retained earnings</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>195,563</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>211,247</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Total stockholders' equity</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>256,144</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>283,379</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Total liabilities and stockholders' equity</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>$365,264</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>$402,392</t>
-        </is>
-      </c>
-    </row>
+    <row r="4"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -1136,7 +539,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Alphabet Inc. CONSOLIDATED STATEMENTS OF INCOME (in millions, except per share amounts) — Alphabet Inc.  (in in millions, except per share amounts)</t>
+          <t>Alphabet Inc. CONSOLIDATED STATEMENTS OF INCOME (in millions, except per share amounts) — Alphabet Inc.  (in millions, except per share amounts)</t>
         </is>
       </c>
     </row>
@@ -1170,296 +573,296 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Revenues</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>$ 257,637</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>$ 282,836</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>$ 307,394</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Costs and expenses:</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Cost of revenues</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>110,939</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>126,203</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>133,332</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Research and development</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>31,562</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>39,500</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>45,427</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sales and marketing</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>22,912</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>26,567</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>27,917</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   General and administrative</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>13,510</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>15,724</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>16,425</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Total costs and expenses</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Total costs and expenses</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>178,923</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>207,994</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>223,101</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Income from operations</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Income from operations</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>78,714</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>74,842</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>84,293</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Other income (expense), net</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Other income (expense), net</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>12,020</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>(3,514)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>1,424</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Income before income taxes</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Income before income taxes</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>90,734</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>71,328</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>85,717</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Provision for income taxes</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Provision for income taxes</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>14,701</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>11,356</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>11,922</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net income</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>$ 76,033</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>$ 59,972</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>$ 73,795</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Basic net income per share of Class A, Class B, and Class C stock</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Basic net income per share of Class A, Class B, and Class C stock</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>$ 5.69</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>$ 4.59</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>$ 5.84</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Diluted net income per share of Class A, Class B, and Class C stock</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Diluted net income per share of Class A, Class B, and Class C stock</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>$ 5.61</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>$ 4.56</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>$ 5.80</t>
         </is>
@@ -1526,250 +929,250 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>$ 76,033</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>$ 59,972</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>$ 73,795</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Other comprehensive income (loss):</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Change in foreign currency translation adjustment</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>(1,442)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>(1,836)</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>735</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Available-for-sale investments:</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      Change in net unrealized gains (losses)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>(1,312)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>(4,720)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>1,344</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Less: reclassification adjustment for net (gains) losses included in net income</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>(64)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>1,007</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>1,168</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Net change, net of income tax benefit (expense) of $394, $1,056, and $(698)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>(1,376)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>(3,713)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>2,512</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Cash flow hedges:</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Other comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>(2,256)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>(5,980)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>3,201</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      Change in net unrealized gains (losses)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>(1,312)</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>(4,720)</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>1,344</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1,275</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      Less: reclassification adjustment for net (gains) losses included in net income</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>(64)</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>1,007</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>1,168</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Net change, net of income tax benefit (expense) of $394, $1,056, and $(698)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>(1,376)</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>(3,713)</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>2,512</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Change in net unrealized gains (losses)</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>1,275</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>168</t>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>(154)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>(1,706)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>(214)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Less: reclassification adjustment for net (gains) losses included in net income</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>(154)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>(1,706)</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>(214)</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Net change, net of income tax benefit (expense) of $(122), $110, and $2</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>(431)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>(46)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Net change, net of income tax benefit (expense) of $(122), $110, and $2</t>
+          <t xml:space="preserve">   Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>(2,256)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>(431)</t>
+          <t>(5,980)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>(46)</t>
+          <t>3,201</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Comprehensive income</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>$ 73,777</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>$ 53,992</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>$ 76,996</t>
         </is>
@@ -1804,7 +1207,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Alphabet Inc. CONSOLIDATED STATEMENTS OF STOCKHOLDERS' EQUITY (in millions) — Alphabet Inc.  (in in millions)</t>
+          <t>Alphabet Inc. CONSOLIDATED STATEMENTS OF STOCKHOLDERS' EQUITY (in millions) — Alphabet Inc.  (in millions)</t>
         </is>
       </c>
     </row>
@@ -1823,34 +1226,34 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>Accumulated Other Comprehensive Income (Loss)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2020</t>
+          <t xml:space="preserve">   Balance as of December 31, 2020</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -1860,244 +1263,244 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;58,510</t>
+          <t>$ 58,510</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;633</t>
+          <t>$ 633</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;163,401</t>
+          <t>$ 163,401</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;222,544</t>
+          <t>$ 222,544</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Stock issued</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Stock issued</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Stock-based compensation expense</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Stock-based compensation expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>15,539</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>15,539</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Tax withholding related to vesting of restricted stock units and other</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tax withholding related to vesting of restricted stock units and other</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>(10,273)</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>(10,273)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Repurchases of stock</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Repurchases of stock</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>(407)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>(2,324)</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>(47,950)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>(50,274)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Sale of interest in consolidated entities</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sale of interest in consolidated entities</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>310</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net income</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>76,033</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>76,033</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>(2,256)</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>(2,256)</t>
         </is>
@@ -2106,7 +1509,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2021</t>
+          <t xml:space="preserve">   Balance as of December 31, 2021</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -2136,224 +1539,224 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Stock issued</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Stock issued</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Stock-based compensation expense</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Stock-based compensation expense</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>19,525</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>19,525</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Tax withholding related to vesting of restricted stock units and other</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tax withholding related to vesting of restricted stock units and other</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>(9,754)</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>(9,755)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Repurchases of stock</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Repurchases of stock</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>(530)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>(3,404)</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>(55,892)</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>(59,296)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Sale of interest in consolidated entities</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sale of interest in consolidated entities</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net income</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>59,972</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>59,972</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>(5,980)</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>(5,980)</t>
         </is>
@@ -2362,7 +1765,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2022</t>
+          <t xml:space="preserve">   Balance as of December 31, 2022</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -2392,192 +1795,192 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Stock issued</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Stock issued</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Stock-based compensation expense</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Stock-based compensation expense</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>22,578</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>22,578</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Tax withholding related to vesting of restricted stock units and other</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tax withholding related to vesting of restricted stock units and other</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>(10,164)</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>(10,155)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Repurchases of stock</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Repurchases of stock</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>(528)</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>(4,064)</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>(58,120)</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>(62,184)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net income</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>73,795</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>73,795</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>3,201</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>3,201</t>
         </is>
@@ -2586,7 +1989,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2023</t>
+          <t xml:space="preserve">   Balance as of December 31, 2023</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -2596,22 +1999,22 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;76,534</t>
+          <t>$ 76,534</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;(4,402)</t>
+          <t>$ (4,402)</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;211,247</t>
+          <t>$ 211,247</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>$&lt;br&gt;283,379</t>
+          <t>$ 283,379</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2045,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Alphabet Inc. CONSOLIDATED STATEMENTS OF CASH FLOWS (in millions) — Alphabet Inc.  (in in millions)</t>
+          <t>Alphabet Inc. CONSOLIDATED STATEMENTS OF CASH FLOWS (in millions) — Alphabet Inc.  (in millions)</t>
         </is>
       </c>
     </row>
@@ -2676,788 +2079,788 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Operating activities</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Net income</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>$76,033</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>$59,972</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>$73,795</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>$ 76,033</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>$ 59,972</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>$ 73,795</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Adjustments:</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      Depreciation of property and equipment</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>10,273</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>13,475</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>11,946</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Stock-based compensation expense</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>15,376</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>19,362</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>22,460</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Deferred income taxes</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>1,808</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>(8,081)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>(7,763)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      (Gain) loss on debt and equity securities, net</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>(12,270)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>5,519</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Other</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>1,955</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>3,483</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>4,330</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Changes in assets and liabilities, net of effects of acquisitions:</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Net cash provided by operating activities</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>91,652</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>91,495</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>101,746</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Depreciation of property and equipment</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>10,273</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>13,475</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>11,946</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Stock-based compensation expense</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>15,376</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>19,362</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>22,460</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Deferred income taxes</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>1,808</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>(8,081)</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>(7,763)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      (Gain) loss on debt and equity securities, net</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>(12,270)</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>5,519</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Other</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>1,955</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>3,483</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>4,330</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>(9,095)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>(2,317)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>(7,833)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accounts receivable, net</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>(9,095)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>(2,317)</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>(7,833)</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Income taxes, net</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>(625)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>523</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Income taxes, net</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>(625)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>523</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Other assets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>(1,846)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>(5,046)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>(2,143)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Other assets</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>(1,846)</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>(5,046)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>(2,143)</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Accounts payable</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>664</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accounts payable</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>664</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Accrued expenses and other liabilities</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>7,304</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>3,915</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>3,937</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accrued expenses and other liabilities</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>7,304</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>3,915</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>3,937</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Accrued revenue share</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>1,682</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>(445)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>482</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Accrued revenue share</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>1,682</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>(445)</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>482</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Deferred revenue</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>525</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Deferred revenue</t>
+          <t xml:space="preserve">   Net cash provided by operating activities</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>91,652</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>91,495</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>101,746</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Investing activities</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Purchases of property and equipment</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>(24,640)</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>(31,485)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>(32,251)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>(135,196)</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>(78,874)</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>(77,858)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Maturities and sales of marketable securities</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>128,294</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>97,822</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>86,672</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Purchases of non-marketable securities</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>(2,838)</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>(2,531)</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>(3,027)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Maturities and sales of non-marketable securities</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>934</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>947</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Acquisitions, net of cash acquired, and purchases of intangible assets</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>(2,618)</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>(6,969)</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>(495)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Other investing activities</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>541</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>1,589</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>(1,051)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   Net cash used in investing activities</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>(35,523)</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>(20,298)</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>(27,063)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Financing activities</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr"/>
-      <c r="D30" s="6" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Net payments related to stock-based award activities</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>(10,162)</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>(9,300)</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>(9,837)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Repurchases of stock</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>(50,274)</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>(59,296)</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>(61,504)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Proceeds from issuance of debt, net of costs</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>20,199</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>52,872</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>10,790</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Repayments of debt</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>(21,435)</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>(54,068)</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>(11,550)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Proceeds from sale of interest in consolidated entities, net</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>310</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   Net cash used in financing activities</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>(61,362)</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>(69,757)</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>(72,093)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Effect of exchange rate changes on cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>(287)</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>(506)</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>(421)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Net increase (decrease) in cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>(5,520)</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>934</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>2,169</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at beginning of period</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>26,465</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>20,945</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>21,879</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>$20,945</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>$21,879</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>$24,048</t>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>$ 20,945</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>$ 21,879</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>$ 24,048</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Supplemental disclosures of cash flow information</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr"/>
-      <c r="C41" s="6" t="inlineStr"/>
-      <c r="D41" s="6" t="inlineStr"/>
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="8" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Cash paid for income taxes, net of refunds</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>$13,412</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>$18,892</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>$19,164</t>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>$ 13,412</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>$ 18,892</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>$ 19,164</t>
         </is>
       </c>
     </row>
